--- a/data/trans_camb/P57_AC_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 3,75</t>
+          <t>-9,35; 3,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,85</t>
+          <t>3,02; 15,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -3,69</t>
+          <t>-17,11; -3,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 10,27</t>
+          <t>-5,9; 10,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 18,98</t>
+          <t>5,03; 18,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -7,51</t>
+          <t>-21,3; -7,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 4,54</t>
+          <t>-6,09; 4,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 15,69</t>
+          <t>6,14; 15,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -8,07</t>
+          <t>-16,73; -7,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 5,81</t>
+          <t>-13,7; 6,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 25,42</t>
+          <t>4,59; 25,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,82; -5,96</t>
+          <t>-24,97; -6,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 16,83</t>
+          <t>-8,38; 16,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 31,13</t>
+          <t>7,47; 31,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,16; -12,43</t>
+          <t>-30,25; -11,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 7,06</t>
+          <t>-8,96; 7,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 24,63</t>
+          <t>8,83; 23,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -12,96</t>
+          <t>-24,58; -12,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 10,81</t>
+          <t>-3,27; 10,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 19,14</t>
+          <t>6,03; 19,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,29</t>
+          <t>-5,67; 8,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 11,88</t>
+          <t>-3,4; 11,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,53</t>
+          <t>4,67; 18,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 3,74</t>
+          <t>-8,76; 4,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,17</t>
+          <t>-1,62; 9,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 16,56</t>
+          <t>7,68; 16,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,25</t>
+          <t>-5,67; 4,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 18,6</t>
+          <t>-4,94; 17,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 33,17</t>
+          <t>9,11; 34,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 14,47</t>
+          <t>-8,54; 14,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 19,53</t>
+          <t>-4,7; 17,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 30,22</t>
+          <t>6,92; 30,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 5,96</t>
+          <t>-12,58; 6,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 13,37</t>
+          <t>-2,3; 14,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 26,96</t>
+          <t>11,7; 27,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 6,89</t>
+          <t>-8,66; 7,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,52; -0,25</t>
+          <t>-11,99; -0,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 17,39</t>
+          <t>7,18; 17,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-58,09; -7,32</t>
+          <t>-55,43; -6,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 9,01</t>
+          <t>-8,47; 9,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 25,27</t>
+          <t>7,71; 24,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 4,89</t>
+          <t>-13,34; 5,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 0,15</t>
+          <t>-9,1; 0,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 17,55</t>
+          <t>8,41; 17,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-51,25; -5,72</t>
+          <t>-54,4; -5,88</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -0,18</t>
+          <t>-16,03; -0,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,24; 25,53</t>
+          <t>9,64; 25,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,02; -10,48</t>
+          <t>-75,74; -8,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 13,89</t>
+          <t>-11,36; 15,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 39,71</t>
+          <t>10,61; 38,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 7,75</t>
+          <t>-17,69; 8,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 0,2</t>
+          <t>-12,29; 0,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,23; 25,74</t>
+          <t>11,52; 24,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,34; -8,03</t>
+          <t>-75,13; -8,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 0,97</t>
+          <t>-6,33; 1,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,9</t>
+          <t>4,7; 12,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -2,27</t>
+          <t>-10,75; -2,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,15</t>
+          <t>-0,12; 9,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 14,25</t>
+          <t>5,88; 14,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -6,91</t>
+          <t>-15,92; -6,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,21</t>
+          <t>-2,47; 3,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 11,99</t>
+          <t>6,49; 11,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; -5,25</t>
+          <t>-11,96; -5,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 1,39</t>
+          <t>-8,72; 1,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 17,23</t>
+          <t>6,49; 17,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -3,36</t>
+          <t>-15,0; -3,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 13,02</t>
+          <t>-0,07; 13,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,02; 20,23</t>
+          <t>7,69; 20,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,06; -9,58</t>
+          <t>-21,0; -9,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 4,58</t>
+          <t>-3,39; 4,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,96; 17,0</t>
+          <t>8,94; 17,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -7,42</t>
+          <t>-16,44; -8,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 6,24</t>
+          <t>-7,52; 6,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,69; 16,04</t>
+          <t>3,63; 15,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 4,1</t>
+          <t>-9,79; 4,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 3,45</t>
+          <t>-6,38; 3,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,77</t>
+          <t>2,68; 11,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,13; -7,74</t>
+          <t>-30,95; -7,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,54</t>
+          <t>-4,9; 2,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,36</t>
+          <t>4,15; 11,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,94; -5,46</t>
+          <t>-22,32; -5,42</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 9,2</t>
+          <t>-9,9; 8,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,76; 24,13</t>
+          <t>4,89; 23,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 6,13</t>
+          <t>-12,93; 6,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 4,57</t>
+          <t>-8,05; 4,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,91; 15,71</t>
+          <t>3,33; 15,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -10,26</t>
+          <t>-39,23; -9,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,46</t>
+          <t>-6,39; 3,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,47</t>
+          <t>5,34; 15,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,38; -7,5</t>
+          <t>-29,66; -7,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 11,36</t>
+          <t>-5,41; 11,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,94; 28,07</t>
+          <t>12,35; 27,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,88; -3,01</t>
+          <t>-25,99; -2,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,31</t>
+          <t>-1,34; 5,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,98; 15,79</t>
+          <t>9,08; 15,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -1,04</t>
+          <t>-9,84; -1,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,65</t>
+          <t>-0,98; 6,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>10,34; 16,95</t>
+          <t>10,93; 17,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -4,45</t>
+          <t>-13,39; -4,2</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 21,34</t>
+          <t>-8,73; 22,27</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19,36; 53,48</t>
+          <t>20,06; 53,06</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,12; -5,42</t>
+          <t>-44,32; -4,98</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 9,48</t>
+          <t>-1,89; 8,97</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,69; 23,71</t>
+          <t>12,77; 23,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -1,53</t>
+          <t>-13,96; -1,57</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,79</t>
+          <t>-1,4; 9,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15,2; 26,2</t>
+          <t>16,05; 26,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,74; -6,73</t>
+          <t>-19,71; -6,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,8</t>
+          <t>-3,8; 0,75</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,42</t>
+          <t>8,77; 13,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,72; -6,02</t>
+          <t>-24,47; -5,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,55</t>
+          <t>0,18; 4,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,32</t>
+          <t>9,29; 13,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -6,95</t>
+          <t>-14,49; -7,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,04</t>
+          <t>-0,94; 2,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,79; 12,67</t>
+          <t>9,71; 12,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -7,24</t>
+          <t>-17,65; -7,25</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,18</t>
+          <t>-5,54; 1,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12,98; 19,89</t>
+          <t>12,51; 19,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,9; -8,81</t>
+          <t>-35,73; -8,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,55</t>
+          <t>0,29; 6,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,65; 19,14</t>
+          <t>12,88; 19,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -10,01</t>
+          <t>-20,49; -10,04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,99</t>
+          <t>-1,34; 3,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,48</t>
+          <t>13,82; 18,82</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -10,5</t>
+          <t>-25,39; -10,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AC_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,62</t>
+          <t>-9,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,15</t>
+          <t>-13,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,35</t>
+          <t>-11,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 3,94</t>
+          <t>-9,63; 4,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,71</t>
+          <t>3,84; 16,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; -3,9</t>
+          <t>-15,79; -3,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 10,2</t>
+          <t>-5,14; 10,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,97</t>
+          <t>4,99; 18,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -7,01</t>
+          <t>-19,67; -5,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 4,6</t>
+          <t>-5,8; 4,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 15,32</t>
+          <t>6,36; 15,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -7,85</t>
+          <t>-16,29; -6,98</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-16,05%</t>
+          <t>-14,6%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,66%</t>
+          <t>-19,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,75%</t>
+          <t>-17,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 6,46</t>
+          <t>-13,88; 7,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 25,24</t>
+          <t>5,52; 25,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -6,39</t>
+          <t>-22,62; -5,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 16,95</t>
+          <t>-7,48; 16,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 31,36</t>
+          <t>7,21; 29,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -11,38</t>
+          <t>-28,18; -9,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 7,26</t>
+          <t>-8,49; 6,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 23,92</t>
+          <t>9,2; 24,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -12,22</t>
+          <t>-23,87; -10,96</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-2,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 10,59</t>
+          <t>-3,71; 10,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 19,71</t>
+          <t>4,98; 19,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 8,47</t>
+          <t>-4,58; 10,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,16</t>
+          <t>-2,77; 11,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 18,73</t>
+          <t>5,65; 18,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 4,09</t>
+          <t>-9,78; 3,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 9,03</t>
+          <t>-1,87; 8,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 16,95</t>
+          <t>7,58; 17,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,43</t>
+          <t>-4,98; 5,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,21%</t>
+          <t>-3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,96%</t>
+          <t>0,07%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 17,96</t>
+          <t>-5,79; 17,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 34,34</t>
+          <t>7,56; 33,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 14,75</t>
+          <t>-6,85; 17,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 17,76</t>
+          <t>-4,02; 18,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 30,38</t>
+          <t>8,31; 30,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 6,42</t>
+          <t>-14,17; 5,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 14,86</t>
+          <t>-2,76; 14,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 27,8</t>
+          <t>11,36; 28,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 7,23</t>
+          <t>-7,46; 8,42</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-32,04</t>
+          <t>-8,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-5,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-26,46</t>
+          <t>-8,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -0,36</t>
+          <t>-11,2; -0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 17,75</t>
+          <t>6,84; 17,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-55,43; -6,25</t>
+          <t>-15,36; -3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 9,75</t>
+          <t>-9,3; 9,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 24,9</t>
+          <t>6,43; 24,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 5,08</t>
+          <t>-14,54; 4,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 0,18</t>
+          <t>-9,25; 0,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 17,25</t>
+          <t>8,84; 17,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-54,4; -5,88</t>
+          <t>-13,21; -2,86</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-44,67%</t>
+          <t>-12,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-6,14%</t>
+          <t>-7,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-37,12%</t>
+          <t>-11,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -0,52</t>
+          <t>-15,14; -0,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 25,85</t>
+          <t>9,09; 25,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,74; -8,66</t>
+          <t>-20,69; -5,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 15,37</t>
+          <t>-12,35; 14,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,61; 38,98</t>
+          <t>9,19; 38,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 8,15</t>
+          <t>-19,47; 6,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 0,26</t>
+          <t>-12,6; 0,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 24,99</t>
+          <t>11,8; 25,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -8,4</t>
+          <t>-17,73; -4,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,77</t>
+          <t>-5,9</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,38</t>
+          <t>-9,73</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,58</t>
+          <t>-7,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,33</t>
+          <t>-6,72; 0,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,13</t>
+          <t>4,6; 11,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -2,28</t>
+          <t>-9,81; -1,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 9,1</t>
+          <t>0,28; 8,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,27</t>
+          <t>6,22; 14,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -6,85</t>
+          <t>-14,23; -5,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,21</t>
+          <t>-2,92; 3,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,96</t>
+          <t>6,47; 11,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -5,65</t>
+          <t>-10,15; -4,25</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-9,57%</t>
+          <t>-8,35%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,55%</t>
+          <t>-13,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,99%</t>
+          <t>-10,32%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 1,94</t>
+          <t>-9,25; 1,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 17,61</t>
+          <t>6,39; 17,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -3,38</t>
+          <t>-13,67; -2,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 13,08</t>
+          <t>0,33; 12,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,69; 20,23</t>
+          <t>8,22; 20,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,0; -9,72</t>
+          <t>-18,82; -7,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 4,6</t>
+          <t>-4,01; 4,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 17,08</t>
+          <t>8,8; 16,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -8,02</t>
+          <t>-13,94; -5,94</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-16,19</t>
+          <t>-6,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-11,25</t>
+          <t>-5,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 6,0</t>
+          <t>-6,39; 6,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,43</t>
+          <t>4,24; 15,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 4,23</t>
+          <t>-9,07; 3,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,14</t>
+          <t>-6,39; 2,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 11,48</t>
+          <t>2,61; 11,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -7,47</t>
+          <t>-10,9; -1,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,37</t>
+          <t>-5,22; 2,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,15; 11,33</t>
+          <t>4,31; 11,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -5,42</t>
+          <t>-8,76; -1,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,02%</t>
+          <t>-3,53%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,88%</t>
+          <t>-8,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-14,98%</t>
+          <t>-6,72%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 8,73</t>
+          <t>-8,67; 9,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,89; 23,45</t>
+          <t>5,32; 24,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 6,34</t>
+          <t>-12,14; 5,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 4,18</t>
+          <t>-8,11; 3,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,33; 15,34</t>
+          <t>3,19; 15,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,23; -9,73</t>
+          <t>-13,44; -2,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,22</t>
+          <t>-6,72; 3,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,34; 15,6</t>
+          <t>5,54; 15,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,66; -7,25</t>
+          <t>-11,26; -1,83</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-15,25</t>
+          <t>-11,88</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,55</t>
+          <t>-4,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>-6,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 11,48</t>
+          <t>-4,93; 11,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12,35; 27,23</t>
+          <t>12,8; 27,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,99; -2,64</t>
+          <t>-22,55; 0,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,98</t>
+          <t>-0,99; 6,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,08; 15,97</t>
+          <t>9,05; 16,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -1,05</t>
+          <t>-8,29; -0,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,13</t>
+          <t>-0,68; 6,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>10,93; 17,26</t>
+          <t>10,82; 17,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,39; -4,2</t>
+          <t>-11,22; -2,46</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-26,97%</t>
+          <t>-21,01%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-8,04%</t>
+          <t>-6,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-12,81%</t>
+          <t>-9,69%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 22,27</t>
+          <t>-8,2; 20,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20,06; 53,06</t>
+          <t>21,06; 54,63</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-44,32; -4,98</t>
+          <t>-38,74; -0,4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,97</t>
+          <t>-1,4; 9,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,77; 23,84</t>
+          <t>12,72; 23,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,96; -1,57</t>
+          <t>-11,76; -0,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,41</t>
+          <t>-1,0; 9,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16,05; 26,85</t>
+          <t>15,77; 26,93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -6,45</t>
+          <t>-16,68; -3,78</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,25</t>
+          <t>-5,6</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-6,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-10,48</t>
+          <t>-6,17</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,75</t>
+          <t>-4,01; 0,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,16</t>
+          <t>9,05; 13,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,47; -5,87</t>
+          <t>-8,04; -3,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,63</t>
+          <t>0,2; 4,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,49</t>
+          <t>9,41; 13,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -7,07</t>
+          <t>-8,82; -4,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,22</t>
+          <t>-1,12; 2,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,71; 12,9</t>
+          <t>9,61; 12,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -7,25</t>
+          <t>-7,71; -4,46</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-16,56%</t>
+          <t>-8,24%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-13,64%</t>
+          <t>-9,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-15,11%</t>
+          <t>-8,89%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,11</t>
+          <t>-5,82; 1,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12,51; 19,63</t>
+          <t>13,05; 20,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,73; -8,74</t>
+          <t>-11,72; -5,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,65</t>
+          <t>0,28; 6,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,46</t>
+          <t>13,11; 19,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,49; -10,04</t>
+          <t>-12,27; -6,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,25</t>
+          <t>-1,58; 3,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13,82; 18,82</t>
+          <t>13,66; 18,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,39; -10,55</t>
+          <t>-11,03; -6,51</t>
         </is>
       </c>
     </row>
